--- a/public/assets/systems/adaa/ADAA_Portfolio_Target_History.xlsx
+++ b/public/assets/systems/adaa/ADAA_Portfolio_Target_History.xlsx
@@ -219,7 +219,7 @@
         <v>0.120833333333333</v>
       </c>
       <c r="E2" s="1">
-        <v>0.102083333333333</v>
+        <v>0.0729166666666667</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -267,7 +267,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.408333333333333</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="3">

--- a/public/assets/systems/adaa/ADAA_Portfolio_Target_History.xlsx
+++ b/public/assets/systems/adaa/ADAA_Portfolio_Target_History.xlsx
@@ -219,7 +219,7 @@
         <v>0.120833333333333</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0729166666666667</v>
+        <v>0.102083333333333</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -267,7 +267,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0.4375</v>
+        <v>0.408333333333333</v>
       </c>
     </row>
     <row r="3">
